--- a/csv_chiune.xlsx
+++ b/csv_chiune.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/655fb4eea315f23b/Desktop/Information Science and Cultural Heritage/Sugihara_Chiune/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="8_{C1DDC20A-F30D-454C-97E1-A5036A6EB4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{658D827B-B341-4173-BA55-309B08F94FAE}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="8_{C1DDC20A-F30D-454C-97E1-A5036A6EB4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{306C28CA-771A-4DB2-8B09-94322A2BB060}"/>
   <bookViews>
-    <workbookView xWindow="3012" yWindow="3732" windowWidth="17280" windowHeight="9960" xr2:uid="{81F1E1D7-AE78-48BE-AE4C-BEA43D5517B7}"/>
+    <workbookView minimized="1" xWindow="3012" yWindow="3732" windowWidth="17280" windowHeight="9960" xr2:uid="{81F1E1D7-AE78-48BE-AE4C-BEA43D5517B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
